--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK139"/>
+  <dimension ref="A1:AK138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8067,10 +8067,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45906.5625</v>
+        <v>45906.58333333334</v>
       </c>
     </row>
     <row r="95">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45906.58333333334</v>
+        <v>45906.60416666666</v>
       </c>
     </row>
     <row r="99">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45906.60416666666</v>
+        <v>45906.625</v>
       </c>
     </row>
     <row r="100">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13657,27 +13657,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45906.625</v>
+        <v>45906.64583333334</v>
       </c>
     </row>
     <row r="104">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14689,27 +14689,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45906.64583333334</v>
+        <v>45906.66666666666</v>
       </c>
     </row>
     <row r="112">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45906.66666666666</v>
+        <v>45906.6875</v>
       </c>
     </row>
     <row r="116">
@@ -15334,27 +15334,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45906.6875</v>
+        <v>45906.70833333334</v>
       </c>
     </row>
     <row r="117">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45906.70833333334</v>
+        <v>45906.77083333334</v>
       </c>
     </row>
     <row r="123">
@@ -16237,12 +16237,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45906.77083333334</v>
+        <v>45906.83333333334</v>
       </c>
     </row>
     <row r="124">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45906.83333333334</v>
+        <v>45906.85416666666</v>
       </c>
     </row>
     <row r="127">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45906.85416666666</v>
+        <v>45906.875</v>
       </c>
     </row>
     <row r="131">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45906.875</v>
+        <v>45906.89583333334</v>
       </c>
     </row>
     <row r="132">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18034,7 +18034,7 @@
         <v>0</v>
       </c>
       <c r="AK136" s="3" t="n">
-        <v>45906.89583333334</v>
+        <v>45906.91666666666</v>
       </c>
     </row>
     <row r="137">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18172,12 +18172,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18292,135 +18292,6 @@
         <v>0</v>
       </c>
       <c r="AK138" s="3" t="n">
-        <v>45906.91666666666</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>45906</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" t="n">
-        <v>0</v>
-      </c>
-      <c r="W139" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK139" s="3" t="n">
         <v>45906.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G137" t="n">

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK138"/>
+  <dimension ref="A1:AK139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12496,27 +12496,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45906.58333333334</v>
+        <v>45906.5625</v>
       </c>
     </row>
     <row r="95">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45906.60416666666</v>
+        <v>45906.58333333334</v>
       </c>
     </row>
     <row r="99">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45906.625</v>
+        <v>45906.60416666666</v>
       </c>
     </row>
     <row r="100">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45906.64583333334</v>
+        <v>45906.625</v>
       </c>
     </row>
     <row r="104">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45906.66666666666</v>
+        <v>45906.64583333334</v>
       </c>
     </row>
     <row r="112">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15205,27 +15205,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45906.6875</v>
+        <v>45906.66666666666</v>
       </c>
     </row>
     <row r="116">
@@ -15334,27 +15334,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45906.70833333334</v>
+        <v>45906.6875</v>
       </c>
     </row>
     <row r="117">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45906.77083333334</v>
+        <v>45906.70833333334</v>
       </c>
     </row>
     <row r="123">
@@ -16237,12 +16237,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45906.83333333334</v>
+        <v>45906.77083333334</v>
       </c>
     </row>
     <row r="124">
@@ -16624,7 +16624,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45906.85416666666</v>
+        <v>45906.83333333334</v>
       </c>
     </row>
     <row r="127">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45906.875</v>
+        <v>45906.85416666666</v>
       </c>
     </row>
     <row r="131">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45906.89583333334</v>
+        <v>45906.875</v>
       </c>
     </row>
     <row r="132">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18034,7 +18034,7 @@
         <v>0</v>
       </c>
       <c r="AK136" s="3" t="n">
-        <v>45906.91666666666</v>
+        <v>45906.89583333334</v>
       </c>
     </row>
     <row r="137">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18172,126 +18172,255 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Loudoun United</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK138" s="3" t="n">
+        <v>45906.91666666666</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45906</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>Bay</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Kansas City</t>
         </is>
       </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="inlineStr">
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="n">
-        <v>0</v>
-      </c>
-      <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" t="n">
-        <v>0</v>
-      </c>
-      <c r="W138" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK138" s="3" t="n">
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK139" s="3" t="n">
         <v>45906.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G136" t="n">

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.46</v>
+        <v>3.14</v>
       </c>
       <c r="M21" t="n">
-        <v>4.33</v>
+        <v>3.52</v>
       </c>
       <c r="N21" t="n">
-        <v>5.86</v>
+        <v>2.01</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7680,10 +7680,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G136" t="n">

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7680,10 +7680,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G136" t="n">

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.14</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>3.52</v>
+        <v>4.33</v>
       </c>
       <c r="N21" t="n">
-        <v>2.01</v>
+        <v>5.86</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.46</v>
+        <v>3.14</v>
       </c>
       <c r="M22" t="n">
-        <v>4.33</v>
+        <v>3.52</v>
       </c>
       <c r="N22" t="n">
-        <v>5.86</v>
+        <v>2.01</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6519,10 +6519,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G138" t="n">

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.46</v>
+        <v>3.14</v>
       </c>
       <c r="M21" t="n">
-        <v>4.33</v>
+        <v>3.52</v>
       </c>
       <c r="N21" t="n">
-        <v>5.86</v>
+        <v>2.01</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.14</v>
+        <v>1.46</v>
       </c>
       <c r="M22" t="n">
-        <v>3.52</v>
+        <v>4.33</v>
       </c>
       <c r="N22" t="n">
-        <v>2.01</v>
+        <v>5.86</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5100,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6519,10 +6519,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G136" t="n">

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.14</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>3.52</v>
+        <v>4.33</v>
       </c>
       <c r="N21" t="n">
-        <v>2.01</v>
+        <v>5.86</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.46</v>
+        <v>3.14</v>
       </c>
       <c r="M22" t="n">
-        <v>4.33</v>
+        <v>3.52</v>
       </c>
       <c r="N22" t="n">
-        <v>5.86</v>
+        <v>2.01</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK139"/>
+  <dimension ref="A1:AK138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="M22" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
         <v>2.01</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4326,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4535,17 +4535,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.02</v>
+        <v>2.22</v>
       </c>
       <c r="M36" t="n">
-        <v>10.2</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>29</v>
+        <v>3.07</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45906.5</v>
+        <v>45906.52083333334</v>
       </c>
     </row>
     <row r="78">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11206,12 +11206,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>45906.52083333334</v>
+        <v>45906.54166666666</v>
       </c>
     </row>
     <row r="85">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11722,27 +11722,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45906.54166666666</v>
+        <v>45906.5625</v>
       </c>
     </row>
     <row r="89">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45906.5625</v>
+        <v>45906.58333333334</v>
       </c>
     </row>
     <row r="95">
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13012,27 +13012,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45906.58333333334</v>
+        <v>45906.60416666666</v>
       </c>
     </row>
     <row r="99">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45906.60416666666</v>
+        <v>45906.625</v>
       </c>
     </row>
     <row r="100">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13657,27 +13657,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45906.625</v>
+        <v>45906.64583333334</v>
       </c>
     </row>
     <row r="104">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14560,12 +14560,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45906.64583333334</v>
+        <v>45906.66666666666</v>
       </c>
     </row>
     <row r="111">
@@ -14689,27 +14689,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45906.64583333334</v>
+        <v>45906.66666666666</v>
       </c>
     </row>
     <row r="112">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15076,27 +15076,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45906.66666666666</v>
+        <v>45906.6875</v>
       </c>
     </row>
     <row r="115">
@@ -15205,27 +15205,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45906.66666666666</v>
+        <v>45906.6875</v>
       </c>
     </row>
     <row r="116">
@@ -15334,27 +15334,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45906.6875</v>
+        <v>45906.70833333334</v>
       </c>
     </row>
     <row r="117">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45906.70833333334</v>
+        <v>45906.77083333334</v>
       </c>
     </row>
     <row r="123">
@@ -16237,12 +16237,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45906.77083333334</v>
+        <v>45906.83333333334</v>
       </c>
     </row>
     <row r="124">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45906.83333333334</v>
+        <v>45906.85416666666</v>
       </c>
     </row>
     <row r="127">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45906.85416666666</v>
+        <v>45906.875</v>
       </c>
     </row>
     <row r="131">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45906.875</v>
+        <v>45906.89583333334</v>
       </c>
     </row>
     <row r="132">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18034,7 +18034,7 @@
         <v>0</v>
       </c>
       <c r="AK136" s="3" t="n">
-        <v>45906.89583333334</v>
+        <v>45906.91666666666</v>
       </c>
     </row>
     <row r="137">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18172,12 +18172,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18292,135 +18292,6 @@
         <v>0</v>
       </c>
       <c r="AK138" s="3" t="n">
-        <v>45906.91666666666</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>45906</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" t="n">
-        <v>0</v>
-      </c>
-      <c r="W139" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK139" s="3" t="n">
         <v>45906.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK138"/>
+  <dimension ref="A1:AK137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.46</v>
+        <v>3.08</v>
       </c>
       <c r="M21" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>5.86</v>
+        <v>2.01</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.08</v>
+        <v>1.46</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="N22" t="n">
-        <v>2.01</v>
+        <v>5.86</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.8</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
-        <v>3.95</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>1.6</v>
+        <v>2.94</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>2.67</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>2.98</v>
       </c>
       <c r="N29" t="n">
-        <v>6.4</v>
+        <v>2.44</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.02</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>10.2</v>
+        <v>3.31</v>
       </c>
       <c r="N30" t="n">
-        <v>29</v>
+        <v>3.03</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="M32" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="M33" t="n">
         <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.65</v>
+        <v>1.84</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>1.9</v>
+        <v>3.66</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.9</v>
+        <v>2.03</v>
       </c>
       <c r="M35" t="n">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>2.13</v>
+        <v>3.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>3.39</v>
       </c>
       <c r="N36" t="n">
-        <v>3.07</v>
+        <v>2.84</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="M38" t="n">
-        <v>3.39</v>
+        <v>3.34</v>
       </c>
       <c r="N38" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.01</v>
+        <v>1.47</v>
       </c>
       <c r="M40" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="N40" t="n">
-        <v>3.29</v>
+        <v>6.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.03</v>
+        <v>2.9</v>
       </c>
       <c r="M44" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="N44" t="n">
-        <v>3.25</v>
+        <v>2.13</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.51</v>
+        <v>1.81</v>
       </c>
       <c r="M45" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>2.43</v>
+        <v>3.92</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="M47" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="N47" t="n">
-        <v>2.94</v>
+        <v>3.07</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,14 +6732,14 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.67</v>
+        <v>2.21</v>
       </c>
       <c r="M49" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N49" t="n">
         <v>2.98</v>
       </c>
-      <c r="N49" t="n">
-        <v>2.44</v>
-      </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6906,10 +6906,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.64</v>
+        <v>2.85</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N51" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.84</v>
+        <v>2.47</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="N61" t="n">
-        <v>3.66</v>
+        <v>2.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.45</v>
+        <v>1.59</v>
       </c>
       <c r="M62" t="n">
-        <v>3.07</v>
+        <v>3.56</v>
       </c>
       <c r="N62" t="n">
-        <v>2.6</v>
+        <v>4.75</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11713,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>45906.54166666666</v>
+        <v>45906.5625</v>
       </c>
     </row>
     <row r="88">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45906.5625</v>
+        <v>45906.58333333334</v>
       </c>
     </row>
     <row r="94">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45906.58333333334</v>
+        <v>45906.60416666666</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45906.60416666666</v>
+        <v>45906.625</v>
       </c>
     </row>
     <row r="99">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45906.625</v>
+        <v>45906.64583333334</v>
       </c>
     </row>
     <row r="103">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14431,27 +14431,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45906.64583333334</v>
+        <v>45906.66666666666</v>
       </c>
     </row>
     <row r="110">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14634,10 +14634,10 @@
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14947,27 +14947,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45906.66666666666</v>
+        <v>45906.6875</v>
       </c>
     </row>
     <row r="114">
@@ -15205,27 +15205,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45906.6875</v>
+        <v>45906.70833333334</v>
       </c>
     </row>
     <row r="116">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45906.70833333334</v>
+        <v>45906.77083333334</v>
       </c>
     </row>
     <row r="122">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45906.77083333334</v>
+        <v>45906.83333333334</v>
       </c>
     </row>
     <row r="123">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16495,12 +16495,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45906.83333333334</v>
+        <v>45906.85416666666</v>
       </c>
     </row>
     <row r="126">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45906.85416666666</v>
+        <v>45906.875</v>
       </c>
     </row>
     <row r="130">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45906.875</v>
+        <v>45906.89583333334</v>
       </c>
     </row>
     <row r="131">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17785,12 +17785,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17905,7 +17905,7 @@
         <v>0</v>
       </c>
       <c r="AK135" s="3" t="n">
-        <v>45906.89583333334</v>
+        <v>45906.91666666666</v>
       </c>
     </row>
     <row r="136">
@@ -18043,12 +18043,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18163,135 +18163,6 @@
         <v>0</v>
       </c>
       <c r="AK137" s="3" t="n">
-        <v>45906.91666666666</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>45906</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="n">
-        <v>0</v>
-      </c>
-      <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" t="n">
-        <v>0</v>
-      </c>
-      <c r="W138" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK138" s="3" t="n">
         <v>45906.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK137"/>
+  <dimension ref="A1:AK136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.08</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="N21" t="n">
-        <v>2.01</v>
+        <v>5.86</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.46</v>
+        <v>3.08</v>
       </c>
       <c r="M22" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>5.86</v>
+        <v>2.01</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.94</v>
+        <v>6.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.67</v>
+        <v>2.17</v>
       </c>
       <c r="M29" t="n">
-        <v>2.98</v>
+        <v>3.38</v>
       </c>
       <c r="N29" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.05</v>
+        <v>2.67</v>
       </c>
       <c r="M30" t="n">
-        <v>3.31</v>
+        <v>2.98</v>
       </c>
       <c r="N30" t="n">
-        <v>3.03</v>
+        <v>2.44</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="M31" t="n">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.64</v>
+        <v>2.45</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>3.07</v>
       </c>
       <c r="N32" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.43</v>
+        <v>1.84</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>6.4</v>
+        <v>3.66</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="M36" t="n">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>2.84</v>
+        <v>1.92</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="M38" t="n">
-        <v>3.34</v>
+        <v>3.19</v>
       </c>
       <c r="N38" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>3.39</v>
       </c>
       <c r="N41" t="n">
-        <v>5.5</v>
+        <v>2.84</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.8</v>
+        <v>1.44</v>
       </c>
       <c r="M43" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Z43" t="n">
         <v>1.95</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.65</v>
+        <v>2.22</v>
       </c>
       <c r="M46" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="N46" t="n">
-        <v>1.9</v>
+        <v>3.07</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="M47" t="n">
-        <v>2.9</v>
+        <v>3.56</v>
       </c>
       <c r="N47" t="n">
-        <v>3.07</v>
+        <v>4.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.21</v>
+        <v>2.51</v>
       </c>
       <c r="M49" t="n">
-        <v>3.01</v>
+        <v>3.23</v>
       </c>
       <c r="N49" t="n">
-        <v>2.98</v>
+        <v>2.43</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.02</v>
+        <v>4.8</v>
       </c>
       <c r="M50" t="n">
-        <v>10.2</v>
+        <v>3.95</v>
       </c>
       <c r="N50" t="n">
-        <v>29</v>
+        <v>1.6</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,16 +6900,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7244,17 +7244,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.6</v>
+        <v>1.02</v>
       </c>
       <c r="M53" t="n">
-        <v>3.55</v>
+        <v>10.2</v>
       </c>
       <c r="N53" t="n">
-        <v>1.92</v>
+        <v>29</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,16 +7287,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.44</v>
+        <v>2.85</v>
       </c>
       <c r="M54" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="N54" t="n">
-        <v>5.8</v>
+        <v>2.2</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.45</v>
+        <v>1.43</v>
       </c>
       <c r="M55" t="n">
-        <v>3.07</v>
+        <v>4.4</v>
       </c>
       <c r="N55" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.51</v>
+        <v>1.97</v>
       </c>
       <c r="M57" t="n">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="N57" t="n">
-        <v>2.43</v>
+        <v>3.2</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.59</v>
+        <v>2.47</v>
       </c>
       <c r="M62" t="n">
-        <v>3.56</v>
+        <v>3.16</v>
       </c>
       <c r="N62" t="n">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="M63" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N63" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,22 +11727,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14302,27 +14302,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45906.64583333334</v>
+        <v>45906.66666666666</v>
       </c>
     </row>
     <row r="109">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="M110" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="N110" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14634,16 +14634,16 @@
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="M111" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="N111" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14763,10 +14763,10 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y111" t="n">
         <v>0</v>
@@ -14818,27 +14818,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45906.66666666666</v>
+        <v>45906.6875</v>
       </c>
     </row>
     <row r="113">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15076,27 +15076,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45906.6875</v>
+        <v>45906.70833333334</v>
       </c>
     </row>
     <row r="115">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45906.70833333334</v>
+        <v>45906.77083333334</v>
       </c>
     </row>
     <row r="121">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45906.77083333334</v>
+        <v>45906.83333333334</v>
       </c>
     </row>
     <row r="122">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16366,12 +16366,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45906.83333333334</v>
+        <v>45906.85416666666</v>
       </c>
     </row>
     <row r="125">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16882,12 +16882,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45906.85416666666</v>
+        <v>45906.875</v>
       </c>
     </row>
     <row r="129">
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17097,10 +17097,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45906.875</v>
+        <v>45906.89583333334</v>
       </c>
     </row>
     <row r="130">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17355,10 +17355,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17656,12 +17656,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="AK134" s="3" t="n">
-        <v>45906.89583333334</v>
+        <v>45906.91666666666</v>
       </c>
     </row>
     <row r="135">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17865,10 +17865,10 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA135" t="n">
         <v>0</v>
@@ -17914,12 +17914,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18034,135 +18034,6 @@
         <v>0</v>
       </c>
       <c r="AK136" s="3" t="n">
-        <v>45906.91666666666</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>45906</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="n">
-        <v>0</v>
-      </c>
-      <c r="T137" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" t="n">
-        <v>0</v>
-      </c>
-      <c r="W137" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK137" s="3" t="n">
         <v>45906.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.46</v>
+        <v>3.08</v>
       </c>
       <c r="M21" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>5.86</v>
+        <v>2.01</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.08</v>
+        <v>1.46</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="N22" t="n">
-        <v>2.01</v>
+        <v>5.86</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="M29" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.67</v>
+        <v>1.44</v>
       </c>
       <c r="M30" t="n">
-        <v>2.98</v>
+        <v>4.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.44</v>
+        <v>5.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z30" t="n">
         <v>1.95</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.75</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,49 +4410,49 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
         <v>2.05</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.86</v>
-      </c>
       <c r="Z31" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.45</v>
+        <v>1.59</v>
       </c>
       <c r="M32" t="n">
-        <v>3.07</v>
+        <v>3.56</v>
       </c>
       <c r="N32" t="n">
-        <v>2.6</v>
+        <v>4.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.6</v>
+        <v>2.21</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>3.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.92</v>
+        <v>2.98</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5309,17 +5309,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M38" t="n">
-        <v>3.19</v>
+        <v>3.55</v>
       </c>
       <c r="N38" t="n">
-        <v>2.94</v>
+        <v>1.92</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="M39" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>3.25</v>
+        <v>3.92</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5961,10 +5961,10 @@
         <v>1.44</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="M47" t="n">
-        <v>3.56</v>
+        <v>4.4</v>
       </c>
       <c r="N47" t="n">
-        <v>4.75</v>
+        <v>6.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="M50" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N50" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.81</v>
+        <v>1.02</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>10.2</v>
       </c>
       <c r="N52" t="n">
-        <v>3.92</v>
+        <v>29</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,16 +7158,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.02</v>
+        <v>2.01</v>
       </c>
       <c r="M53" t="n">
-        <v>10.2</v>
+        <v>3.14</v>
       </c>
       <c r="N53" t="n">
-        <v>29</v>
+        <v>3.29</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,16 +7287,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.85</v>
+        <v>1.47</v>
       </c>
       <c r="M54" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="N54" t="n">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.43</v>
+        <v>3.65</v>
       </c>
       <c r="M55" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="N55" t="n">
-        <v>6.4</v>
+        <v>1.9</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="M56" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="N56" t="n">
-        <v>4.6</v>
+        <v>2.94</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="M57" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="N57" t="n">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.44</v>
+        <v>2.67</v>
       </c>
       <c r="M58" t="n">
-        <v>4.1</v>
+        <v>2.98</v>
       </c>
       <c r="N58" t="n">
-        <v>5.5</v>
+        <v>2.44</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="M59" t="n">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="N59" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.47</v>
+        <v>2.12</v>
       </c>
       <c r="M62" t="n">
-        <v>3.16</v>
+        <v>3.39</v>
       </c>
       <c r="N62" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14505,10 +14505,10 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14763,10 +14763,10 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.74</v>
+        <v>3</v>
       </c>
       <c r="M122" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N122" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="M129" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="N129" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17097,10 +17097,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17226,10 +17226,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="M131" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="N131" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17355,10 +17355,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.74</v>
+        <v>2.42</v>
       </c>
       <c r="M7" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>2.46</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.08</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="N21" t="n">
-        <v>2.01</v>
+        <v>5.86</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.46</v>
+        <v>3.08</v>
       </c>
       <c r="M22" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>5.86</v>
+        <v>2.01</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.64</v>
+        <v>2.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>2.13</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="M30" t="n">
-        <v>4.3</v>
+        <v>10.2</v>
       </c>
       <c r="N30" t="n">
-        <v>5.8</v>
+        <v>29</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.76</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="M31" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.47</v>
+        <v>1.44</v>
       </c>
       <c r="M35" t="n">
-        <v>3.16</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.58</v>
+        <v>2.07</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5309,17 +5309,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.6</v>
+        <v>1.84</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>1.92</v>
+        <v>3.66</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.51</v>
+        <v>1.47</v>
       </c>
       <c r="M40" t="n">
-        <v>3.23</v>
+        <v>4.4</v>
       </c>
       <c r="N40" t="n">
-        <v>2.43</v>
+        <v>6.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="N43" t="n">
-        <v>5.5</v>
+        <v>3.29</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.84</v>
+        <v>2.51</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N45" t="n">
-        <v>3.66</v>
+        <v>2.43</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.43</v>
+        <v>2.03</v>
       </c>
       <c r="M47" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="N47" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="M48" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="N48" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="M50" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="N50" t="n">
-        <v>2.2</v>
+        <v>3.07</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.02</v>
+        <v>1.59</v>
       </c>
       <c r="M52" t="n">
-        <v>10.2</v>
+        <v>3.56</v>
       </c>
       <c r="N52" t="n">
-        <v>29</v>
+        <v>4.75</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,16 +7158,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="M53" t="n">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="N53" t="n">
-        <v>3.29</v>
+        <v>2.75</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="M54" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>6.2</v>
+        <v>3.92</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="M56" t="n">
-        <v>3.19</v>
+        <v>3.07</v>
       </c>
       <c r="N56" t="n">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.05</v>
+        <v>2.67</v>
       </c>
       <c r="M57" t="n">
-        <v>3.31</v>
+        <v>2.98</v>
       </c>
       <c r="N57" t="n">
-        <v>3.03</v>
+        <v>2.44</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.67</v>
+        <v>2.05</v>
       </c>
       <c r="M58" t="n">
-        <v>2.98</v>
+        <v>3.31</v>
       </c>
       <c r="N58" t="n">
-        <v>2.44</v>
+        <v>3.03</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="M59" t="n">
-        <v>3.55</v>
+        <v>3.19</v>
       </c>
       <c r="N59" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="M61" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="N61" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="N62" t="n">
-        <v>2.84</v>
+        <v>1.92</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,22 +11727,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3</v>
+        <v>1.74</v>
       </c>
       <c r="M122" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N122" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.74</v>
+        <v>3</v>
       </c>
       <c r="M123" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N123" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M130" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N130" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17226,10 +17226,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="M131" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N131" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="M132" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N132" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,16 +17478,16 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>2.17</v>
       </c>
       <c r="M6" t="n">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="N21" t="n">
-        <v>5.86</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.28</v>
+        <v>3.95</v>
       </c>
       <c r="N29" t="n">
-        <v>2.13</v>
+        <v>1.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4326,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="M31" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="N31" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4922,17 +4922,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.44</v>
+        <v>3.6</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>5.5</v>
+        <v>1.92</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="N38" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.64</v>
+        <v>2.01</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="N39" t="n">
-        <v>4.6</v>
+        <v>3.29</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="M42" t="n">
-        <v>3.95</v>
+        <v>3.28</v>
       </c>
       <c r="N42" t="n">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="M43" t="n">
-        <v>3.14</v>
+        <v>3.56</v>
       </c>
       <c r="N43" t="n">
-        <v>3.29</v>
+        <v>4.75</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M45" t="n">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
       <c r="N45" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.12</v>
+        <v>2.67</v>
       </c>
       <c r="M46" t="n">
-        <v>3.39</v>
+        <v>2.98</v>
       </c>
       <c r="N46" t="n">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.03</v>
+        <v>2.47</v>
       </c>
       <c r="M47" t="n">
-        <v>3.55</v>
+        <v>3.16</v>
       </c>
       <c r="N47" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M48" t="n">
         <v>3.65</v>
       </c>
-      <c r="M48" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N48" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.44</v>
+        <v>3.65</v>
       </c>
       <c r="M49" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="N49" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="M50" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="N50" t="n">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.17</v>
+        <v>4.29</v>
       </c>
       <c r="M53" t="n">
-        <v>3.38</v>
+        <v>3.89</v>
       </c>
       <c r="N53" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.81</v>
+        <v>1.43</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="N54" t="n">
-        <v>3.92</v>
+        <v>6.4</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="M56" t="n">
-        <v>3.07</v>
+        <v>3.39</v>
       </c>
       <c r="N56" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.67</v>
+        <v>2.22</v>
       </c>
       <c r="M57" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="N57" t="n">
-        <v>2.44</v>
+        <v>3.07</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="M58" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="N58" t="n">
-        <v>3.03</v>
+        <v>3.66</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.47</v>
+        <v>1.64</v>
       </c>
       <c r="M61" t="n">
-        <v>3.16</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.6</v>
+        <v>2.51</v>
       </c>
       <c r="M62" t="n">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="N62" t="n">
-        <v>1.92</v>
+        <v>2.43</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,10 +14376,10 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="M109" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="N109" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14505,16 +14505,16 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17097,10 +17097,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="M130" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N130" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="M131" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N131" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,16 +17349,16 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M132" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N132" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17484,10 +17484,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17613,10 +17613,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.74</v>
+        <v>2.42</v>
       </c>
       <c r="M5" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.17</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.29</v>
+        <v>3.08</v>
       </c>
       <c r="M21" t="n">
-        <v>5.25</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>2.01</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.08</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.01</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.21</v>
+        <v>4.29</v>
       </c>
       <c r="M27" t="n">
-        <v>3.01</v>
+        <v>3.89</v>
       </c>
       <c r="N27" t="n">
-        <v>2.98</v>
+        <v>1.62</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="M32" t="n">
-        <v>3.38</v>
+        <v>3.14</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>3.29</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4922,17 +4922,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.6</v>
+        <v>1.02</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>10.2</v>
       </c>
       <c r="N35" t="n">
-        <v>1.92</v>
+        <v>29</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="M37" t="n">
         <v>4.4</v>
       </c>
       <c r="N37" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="M38" t="n">
-        <v>3.34</v>
+        <v>4.4</v>
       </c>
       <c r="N38" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M42" t="n">
         <v>2.9</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.28</v>
-      </c>
       <c r="N42" t="n">
-        <v>2.13</v>
+        <v>3.07</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.59</v>
+        <v>2.9</v>
       </c>
       <c r="M43" t="n">
-        <v>3.56</v>
+        <v>3.28</v>
       </c>
       <c r="N43" t="n">
-        <v>4.75</v>
+        <v>2.13</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="M45" t="n">
-        <v>3.07</v>
+        <v>3.55</v>
       </c>
       <c r="N45" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.67</v>
+        <v>1.59</v>
       </c>
       <c r="M46" t="n">
-        <v>2.98</v>
+        <v>3.56</v>
       </c>
       <c r="N46" t="n">
-        <v>2.44</v>
+        <v>4.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6470,17 +6470,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.47</v>
+        <v>3.6</v>
       </c>
       <c r="M47" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="N47" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.85</v>
+        <v>1.44</v>
       </c>
       <c r="M48" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N48" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="M49" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="N49" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.81</v>
+        <v>3.65</v>
       </c>
       <c r="M51" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N51" t="n">
-        <v>3.92</v>
+        <v>1.9</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>4.29</v>
+        <v>2.85</v>
       </c>
       <c r="M53" t="n">
-        <v>3.89</v>
+        <v>3.65</v>
       </c>
       <c r="N53" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="M54" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>6.4</v>
+        <v>3.92</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.12</v>
+        <v>2.47</v>
       </c>
       <c r="M56" t="n">
-        <v>3.39</v>
+        <v>3.16</v>
       </c>
       <c r="N56" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.22</v>
+        <v>2.51</v>
       </c>
       <c r="M57" t="n">
-        <v>2.9</v>
+        <v>3.23</v>
       </c>
       <c r="N57" t="n">
-        <v>3.07</v>
+        <v>2.43</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="M58" t="n">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="N58" t="n">
-        <v>3.66</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.15</v>
+        <v>2.67</v>
       </c>
       <c r="M59" t="n">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="N59" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="N61" t="n">
-        <v>4.6</v>
+        <v>2.94</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.51</v>
+        <v>2.12</v>
       </c>
       <c r="M62" t="n">
-        <v>3.23</v>
+        <v>3.39</v>
       </c>
       <c r="N62" t="n">
-        <v>2.43</v>
+        <v>2.84</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,22 +11727,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,10 +14376,10 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14634,10 +14634,10 @@
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.68</v>
+        <v>2.42</v>
       </c>
       <c r="M124" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N124" t="n">
-        <v>4.1</v>
+        <v>2.65</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M131" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N131" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17355,10 +17355,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M132" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N132" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17484,10 +17484,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="M134" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N134" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z134" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="M135" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N135" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17865,10 +17865,10 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA135" t="n">
         <v>0</v>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.17</v>
+        <v>1.74</v>
       </c>
       <c r="M2" t="n">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.58</v>
+        <v>2.17</v>
       </c>
       <c r="M4" t="n">
-        <v>3.27</v>
+        <v>3.19</v>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.29</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.89</v>
+        <v>3.07</v>
       </c>
       <c r="N27" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="M32" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>3.29</v>
+        <v>4.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="N33" t="n">
-        <v>2.98</v>
+        <v>3.07</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="M35" t="n">
-        <v>10.2</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>29</v>
+        <v>5.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.47</v>
+        <v>1.02</v>
       </c>
       <c r="M38" t="n">
-        <v>4.4</v>
+        <v>10.2</v>
       </c>
       <c r="N38" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5358,10 +5358,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.9</v>
+        <v>2.01</v>
       </c>
       <c r="M43" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="N43" t="n">
-        <v>2.13</v>
+        <v>3.29</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.84</v>
+        <v>4.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="N44" t="n">
-        <v>3.66</v>
+        <v>1.6</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M45" t="n">
-        <v>3.55</v>
+        <v>3.31</v>
       </c>
       <c r="N45" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.59</v>
+        <v>3.65</v>
       </c>
       <c r="M46" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="N46" t="n">
-        <v>4.75</v>
+        <v>1.9</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6470,17 +6470,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M51" t="n">
         <v>3.65</v>
       </c>
-      <c r="M51" t="n">
-        <v>3.55</v>
-      </c>
       <c r="N51" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M53" t="n">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="N53" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.81</v>
+        <v>2.67</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="N54" t="n">
-        <v>3.92</v>
+        <v>2.44</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="M56" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="N56" t="n">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.51</v>
+        <v>1.84</v>
       </c>
       <c r="M57" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>2.43</v>
+        <v>3.66</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="M58" t="n">
-        <v>3.07</v>
+        <v>3.39</v>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.67</v>
+        <v>2.17</v>
       </c>
       <c r="M59" t="n">
-        <v>2.98</v>
+        <v>3.38</v>
       </c>
       <c r="N59" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.05</v>
+        <v>2.47</v>
       </c>
       <c r="M60" t="n">
-        <v>3.31</v>
+        <v>3.16</v>
       </c>
       <c r="N60" t="n">
-        <v>3.03</v>
+        <v>2.5</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="M61" t="n">
-        <v>3.19</v>
+        <v>3.55</v>
       </c>
       <c r="N61" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.12</v>
+        <v>1.43</v>
       </c>
       <c r="M62" t="n">
-        <v>3.39</v>
+        <v>4.4</v>
       </c>
       <c r="N62" t="n">
-        <v>2.84</v>
+        <v>6.4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,22 +11727,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14634,10 +14634,10 @@
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="M111" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="N111" t="n">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14763,16 +14763,16 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3</v>
+        <v>1.74</v>
       </c>
       <c r="M123" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N123" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.68</v>
+        <v>2.42</v>
       </c>
       <c r="M127" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N127" t="n">
-        <v>4.1</v>
+        <v>2.65</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17097,10 +17097,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="M130" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N130" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,16 +17220,16 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="M132" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N132" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,16 +17478,16 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17613,10 +17613,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="M4" t="n">
-        <v>3.19</v>
+        <v>3.33</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>3.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.07</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.44</v>
+        <v>4.8</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N28" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Z28" t="n">
         <v>1.95</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.29</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
-        <v>3.89</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>1.62</v>
+        <v>6.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="M30" t="n">
-        <v>3.56</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.64</v>
+        <v>2.21</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="N32" t="n">
-        <v>4.6</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.22</v>
+        <v>4.29</v>
       </c>
       <c r="M33" t="n">
-        <v>2.9</v>
+        <v>3.89</v>
       </c>
       <c r="N33" t="n">
-        <v>3.07</v>
+        <v>1.62</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.44</v>
+        <v>2.47</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>3.16</v>
       </c>
       <c r="N35" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.07</v>
+        <v>1.58</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N36" t="n">
-        <v>1.92</v>
+        <v>3.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5358,10 +5358,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5696,17 +5696,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="M43" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>3.29</v>
+        <v>4.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.8</v>
+        <v>2.03</v>
       </c>
       <c r="M44" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="N44" t="n">
-        <v>1.6</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="M45" t="n">
-        <v>3.31</v>
+        <v>3.56</v>
       </c>
       <c r="N45" t="n">
-        <v>3.03</v>
+        <v>4.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.65</v>
+        <v>2.22</v>
       </c>
       <c r="M46" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="N46" t="n">
-        <v>1.9</v>
+        <v>3.07</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="M51" t="n">
-        <v>3.65</v>
+        <v>3.39</v>
       </c>
       <c r="N51" t="n">
-        <v>2.2</v>
+        <v>2.84</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.51</v>
+        <v>2.17</v>
       </c>
       <c r="M52" t="n">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
       <c r="N52" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.9</v>
+        <v>1.02</v>
       </c>
       <c r="M53" t="n">
-        <v>3.28</v>
+        <v>10.2</v>
       </c>
       <c r="N53" t="n">
-        <v>2.13</v>
+        <v>29</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,16 +7287,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="M54" t="n">
-        <v>2.98</v>
+        <v>3.65</v>
       </c>
       <c r="N54" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,49 +7506,49 @@
         </is>
       </c>
       <c r="L55" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
         <v>1.81</v>
       </c>
-      <c r="M55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N55" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Z55" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="M56" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>2.94</v>
+        <v>3.92</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="N57" t="n">
-        <v>3.66</v>
+        <v>2.6</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.12</v>
+        <v>2.67</v>
       </c>
       <c r="M58" t="n">
-        <v>3.39</v>
+        <v>2.98</v>
       </c>
       <c r="N58" t="n">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="M59" t="n">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="N59" t="n">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="M60" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="N60" t="n">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="M61" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>3.25</v>
+        <v>3.66</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,22 +11727,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="M108" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="N108" t="n">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,16 +14376,16 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14763,10 +14763,10 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y111" t="n">
         <v>0</v>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3</v>
+        <v>1.74</v>
       </c>
       <c r="M122" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N122" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="M129" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="N129" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17097,10 +17097,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="M130" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="N130" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17226,10 +17226,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="M134" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N134" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="M135" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N135" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17865,10 +17865,10 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA135" t="n">
         <v>0</v>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK136"/>
+  <dimension ref="A1:AK137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="M5" t="n">
-        <v>3.19</v>
+        <v>3.33</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.58</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.08</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.01</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.29</v>
+        <v>3.08</v>
       </c>
       <c r="M22" t="n">
-        <v>5.25</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>2.01</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.65</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>3.39</v>
       </c>
       <c r="N27" t="n">
-        <v>1.9</v>
+        <v>2.84</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>2.47</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>3.16</v>
       </c>
       <c r="N29" t="n">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>3.56</v>
       </c>
       <c r="N30" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="M31" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="N31" t="n">
-        <v>3.29</v>
+        <v>2.43</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.21</v>
+        <v>2.67</v>
       </c>
       <c r="M32" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>2.44</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.29</v>
+        <v>4.8</v>
       </c>
       <c r="M33" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="N33" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.47</v>
+        <v>1.81</v>
       </c>
       <c r="M35" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3.92</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.97</v>
+        <v>4.2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.34</v>
+        <v>3.85</v>
       </c>
       <c r="N36" t="n">
-        <v>3.2</v>
+        <v>1.72</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="M37" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N37" t="n">
-        <v>2.43</v>
+        <v>3.03</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5574,10 +5574,10 @@
         <v>1.44</v>
       </c>
       <c r="M40" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5696,17 +5696,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="M41" t="n">
         <v>3.55</v>
       </c>
       <c r="N41" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="M44" t="n">
-        <v>3.55</v>
+        <v>3.19</v>
       </c>
       <c r="N44" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="M45" t="n">
-        <v>3.56</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>4.75</v>
+        <v>6.2</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="M46" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N46" t="n">
-        <v>3.07</v>
+        <v>5.8</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="M49" t="n">
-        <v>4.4</v>
+        <v>3.14</v>
       </c>
       <c r="N49" t="n">
-        <v>6.2</v>
+        <v>3.29</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6986,17 +6986,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="M51" t="n">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="N51" t="n">
-        <v>2.84</v>
+        <v>1.92</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M54" t="n">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="N54" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.9</v>
+        <v>2.21</v>
       </c>
       <c r="M55" t="n">
-        <v>3.28</v>
+        <v>3.01</v>
       </c>
       <c r="N55" t="n">
-        <v>2.13</v>
+        <v>2.98</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.81</v>
+        <v>2.22</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N56" t="n">
-        <v>3.92</v>
+        <v>3.07</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.15</v>
+        <v>1.43</v>
       </c>
       <c r="M60" t="n">
-        <v>3.19</v>
+        <v>4.4</v>
       </c>
       <c r="N60" t="n">
-        <v>2.94</v>
+        <v>6.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.84</v>
+        <v>1.02</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>10.2</v>
       </c>
       <c r="N61" t="n">
-        <v>3.66</v>
+        <v>29</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,16 +8319,16 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45906.52083333334</v>
+        <v>45906.5</v>
       </c>
     </row>
     <row r="78">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11206,12 +11206,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>45906.54166666666</v>
+        <v>45906.52083333334</v>
       </c>
     </row>
     <row r="85">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11713,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>45906.5625</v>
+        <v>45906.54166666666</v>
       </c>
     </row>
     <row r="88">
@@ -11727,22 +11727,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11892,61 +11892,61 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
@@ -11959,10 +11959,10 @@
         </is>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45906.58333333334</v>
+        <v>45906.5625</v>
       </c>
     </row>
     <row r="94">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45906.60416666666</v>
+        <v>45906.58333333334</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45906.625</v>
+        <v>45906.60416666666</v>
       </c>
     </row>
     <row r="99">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45906.64583333334</v>
+        <v>45906.625</v>
       </c>
     </row>
     <row r="103">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14302,27 +14302,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,10 +14376,10 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45906.66666666666</v>
+        <v>45906.64583333334</v>
       </c>
     </row>
     <row r="109">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.19</v>
+        <v>2.6</v>
       </c>
       <c r="M110" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N110" t="n">
-        <v>3.28</v>
+        <v>2.55</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,61 +14730,61 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD111" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE111" t="inlineStr">
         <is>
@@ -14797,10 +14797,10 @@
         </is>
       </c>
       <c r="AG111" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH111" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
@@ -14818,27 +14818,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="M112" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N112" t="n">
-        <v>2.85</v>
+        <v>1.96</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14892,16 +14892,16 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y112" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45906.6875</v>
+        <v>45906.66666666666</v>
       </c>
     </row>
     <row r="113">
@@ -15076,27 +15076,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45906.70833333334</v>
+        <v>45906.6875</v>
       </c>
     </row>
     <row r="115">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45906.77083333334</v>
+        <v>45906.70833333334</v>
       </c>
     </row>
     <row r="121">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,61 +16020,61 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="M121" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="N121" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V121" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W121" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE121" t="inlineStr">
         <is>
@@ -16087,10 +16087,10 @@
         </is>
       </c>
       <c r="AG121" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH121" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45906.83333333334</v>
+        <v>45906.77083333334</v>
       </c>
     </row>
     <row r="122">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="M124" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N124" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45906.85416666666</v>
+        <v>45906.83333333334</v>
       </c>
     </row>
     <row r="125">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16882,12 +16882,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45906.875</v>
+        <v>45906.85416666666</v>
       </c>
     </row>
     <row r="129">
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17097,10 +17097,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45906.89583333334</v>
+        <v>45906.875</v>
       </c>
     </row>
     <row r="130">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="M130" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="N130" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,16 +17220,16 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="M131" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="N131" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17355,10 +17355,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="M133" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N133" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,16 +17607,16 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -17656,12 +17656,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="AK134" s="3" t="n">
-        <v>45906.91666666666</v>
+        <v>45906.89583333334</v>
       </c>
     </row>
     <row r="135">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="M135" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N135" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17865,10 +17865,10 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="Z135" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AA135" t="n">
         <v>0</v>
@@ -17914,126 +17914,255 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Colorado Springs</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M136" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N136" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" s="3" t="n">
+        <v>45906.91666666666</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45906</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>Bay</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>Kansas City</t>
         </is>
       </c>
-      <c r="G136" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="inlineStr">
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" t="n">
-        <v>0</v>
-      </c>
-      <c r="W136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK136" s="3" t="n">
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK137" s="3" t="n">
         <v>45906.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK137"/>
+  <dimension ref="A1:AK138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="M5" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.58</v>
+        <v>1.74</v>
       </c>
       <c r="M7" t="n">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>3.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>2.84</v>
+        <v>1.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.47</v>
+        <v>1.64</v>
       </c>
       <c r="M29" t="n">
-        <v>3.16</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.59</v>
+        <v>1.97</v>
       </c>
       <c r="M30" t="n">
-        <v>3.56</v>
+        <v>3.34</v>
       </c>
       <c r="N30" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.51</v>
+        <v>1.44</v>
       </c>
       <c r="M31" t="n">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.43</v>
+        <v>5.5</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="M32" t="n">
-        <v>2.98</v>
+        <v>3.28</v>
       </c>
       <c r="N32" t="n">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.45</v>
+        <v>1.43</v>
       </c>
       <c r="M34" t="n">
-        <v>3.07</v>
+        <v>4.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="M36" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="M37" t="n">
-        <v>3.31</v>
+        <v>3.01</v>
       </c>
       <c r="N37" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.64</v>
+        <v>2.22</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N39" t="n">
-        <v>4.6</v>
+        <v>3.07</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.65</v>
+        <v>2.14</v>
       </c>
       <c r="M41" t="n">
         <v>3.55</v>
       </c>
       <c r="N41" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="M42" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="N42" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.97</v>
+        <v>2.47</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="N43" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="M44" t="n">
-        <v>3.19</v>
+        <v>3.55</v>
       </c>
       <c r="N44" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.44</v>
+        <v>4.2</v>
       </c>
       <c r="M46" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="N46" t="n">
-        <v>5.8</v>
+        <v>1.72</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.05</v>
+        <v>1.81</v>
       </c>
       <c r="M47" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>2.2</v>
+        <v>3.92</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="M49" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="N49" t="n">
-        <v>3.29</v>
+        <v>2.94</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,49 +6861,49 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z50" t="n">
         <v>1.84</v>
-      </c>
-      <c r="M50" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N50" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.85</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6986,17 +6986,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.6</v>
+        <v>1.59</v>
       </c>
       <c r="M51" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="N51" t="n">
-        <v>1.92</v>
+        <v>4.75</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.17</v>
+        <v>2.67</v>
       </c>
       <c r="M52" t="n">
-        <v>3.38</v>
+        <v>2.98</v>
       </c>
       <c r="N52" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.9</v>
+        <v>1.13</v>
       </c>
       <c r="M54" t="n">
-        <v>3.28</v>
+        <v>6.8</v>
       </c>
       <c r="N54" t="n">
-        <v>2.13</v>
+        <v>12</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7631,17 +7631,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.22</v>
+        <v>3.6</v>
       </c>
       <c r="M56" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="N56" t="n">
-        <v>3.07</v>
+        <v>1.92</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8067,10 +8067,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.43</v>
+        <v>2.51</v>
       </c>
       <c r="M60" t="n">
-        <v>4.4</v>
+        <v>3.23</v>
       </c>
       <c r="N60" t="n">
-        <v>6.4</v>
+        <v>2.43</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="M61" t="n">
-        <v>10.2</v>
+        <v>4.3</v>
       </c>
       <c r="N61" t="n">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,16 +8319,16 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11722,27 +11722,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,61 +11763,61 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
@@ -11830,10 +11830,10 @@
         </is>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45906.5625</v>
+        <v>45906.54166666666</v>
       </c>
     </row>
     <row r="89">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,61 +11892,61 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
@@ -11959,10 +11959,10 @@
         </is>
       </c>
       <c r="AG89" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,61 +12408,61 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -12496,27 +12496,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45906.58333333334</v>
+        <v>45906.5625</v>
       </c>
     </row>
     <row r="95">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45906.60416666666</v>
+        <v>45906.58333333334</v>
       </c>
     </row>
     <row r="99">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45906.625</v>
+        <v>45906.60416666666</v>
       </c>
     </row>
     <row r="100">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45906.64583333334</v>
+        <v>45906.625</v>
       </c>
     </row>
     <row r="104">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45906.66666666666</v>
+        <v>45906.64583333334</v>
       </c>
     </row>
     <row r="110">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="M110" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="N110" t="n">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14634,16 +14634,16 @@
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="M112" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="N112" t="n">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14892,16 +14892,16 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45906.6875</v>
+        <v>45906.66666666666</v>
       </c>
     </row>
     <row r="114">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15205,27 +15205,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45906.70833333334</v>
+        <v>45906.6875</v>
       </c>
     </row>
     <row r="116">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,61 +16020,61 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X121" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="inlineStr">
         <is>
@@ -16087,10 +16087,10 @@
         </is>
       </c>
       <c r="AG121" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH121" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45906.77083333334</v>
+        <v>45906.70833333334</v>
       </c>
     </row>
     <row r="122">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,61 +16149,61 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S122" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T122" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U122" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W122" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X122" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE122" t="inlineStr">
         <is>
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="AG122" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH122" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45906.83333333334</v>
+        <v>45906.77083333334</v>
       </c>
     </row>
     <row r="123">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3</v>
+        <v>1.74</v>
       </c>
       <c r="M124" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N124" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45906.85416666666</v>
+        <v>45906.83333333334</v>
       </c>
     </row>
     <row r="126">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45906.875</v>
+        <v>45906.85416666666</v>
       </c>
     </row>
     <row r="130">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45906.89583333334</v>
+        <v>45906.875</v>
       </c>
     </row>
     <row r="131">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="M131" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="N131" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,16 +17349,16 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA131" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="M132" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N132" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="M133" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="N133" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17613,10 +17613,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -17785,12 +17785,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="M135" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N135" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17865,16 +17865,16 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -17905,7 +17905,7 @@
         <v>0</v>
       </c>
       <c r="AK135" s="3" t="n">
-        <v>45906.91666666666</v>
+        <v>45906.89583333334</v>
       </c>
     </row>
     <row r="136">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -17955,13 +17955,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="M136" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N136" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -17994,10 +17994,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="Z136" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -18043,126 +18043,255 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Colorado Springs</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M137" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N137" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK137" s="3" t="n">
+        <v>45906.91666666666</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45906</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>Bay</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>Kansas City</t>
         </is>
       </c>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="inlineStr">
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="n">
-        <v>0</v>
-      </c>
-      <c r="T137" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" t="n">
-        <v>0</v>
-      </c>
-      <c r="W137" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK137" s="3" t="n">
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK138" s="3" t="n">
         <v>45906.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.82</v>
+        <v>2.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.29</v>
+        <v>3.08</v>
       </c>
       <c r="M21" t="n">
-        <v>5.25</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>2.01</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.08</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.01</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N27" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.85</v>
+        <v>1.44</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.64</v>
+        <v>2.22</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>3.07</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.97</v>
+        <v>3.05</v>
       </c>
       <c r="M30" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.44</v>
+        <v>2.21</v>
       </c>
       <c r="M31" t="n">
-        <v>4.1</v>
+        <v>3.01</v>
       </c>
       <c r="N31" t="n">
-        <v>5.5</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.9</v>
+        <v>1.59</v>
       </c>
       <c r="M32" t="n">
-        <v>3.28</v>
+        <v>3.56</v>
       </c>
       <c r="N32" t="n">
-        <v>2.13</v>
+        <v>4.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.8</v>
+        <v>1.97</v>
       </c>
       <c r="M33" t="n">
-        <v>3.95</v>
+        <v>3.34</v>
       </c>
       <c r="N33" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="M34" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.88</v>
+        <v>2.9</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="N35" t="n">
-        <v>3.7</v>
+        <v>2.13</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Z35" t="n">
         <v>1.89</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.05</v>
+        <v>2.01</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="N36" t="n">
-        <v>2.2</v>
+        <v>3.29</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.21</v>
+        <v>1.64</v>
       </c>
       <c r="M37" t="n">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>2.98</v>
+        <v>4.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.45</v>
+        <v>1.43</v>
       </c>
       <c r="M38" t="n">
-        <v>3.07</v>
+        <v>4.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.22</v>
+        <v>2.47</v>
       </c>
       <c r="M39" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="N39" t="n">
-        <v>3.07</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="M41" t="n">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="N41" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.01</v>
+        <v>1.47</v>
       </c>
       <c r="M42" t="n">
-        <v>3.14</v>
+        <v>4.3</v>
       </c>
       <c r="N42" t="n">
-        <v>3.29</v>
+        <v>4.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="M44" t="n">
-        <v>3.55</v>
+        <v>3.19</v>
       </c>
       <c r="N44" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="N46" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.81</v>
+        <v>1.13</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="N47" t="n">
-        <v>3.92</v>
+        <v>12</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="M48" t="n">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="N48" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="M49" t="n">
-        <v>3.19</v>
+        <v>4.3</v>
       </c>
       <c r="N49" t="n">
-        <v>2.94</v>
+        <v>5.8</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="M50" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="N50" t="n">
-        <v>3.03</v>
+        <v>3.66</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.47</v>
+        <v>1.02</v>
       </c>
       <c r="M53" t="n">
-        <v>4.3</v>
+        <v>10.2</v>
       </c>
       <c r="N53" t="n">
-        <v>4.7</v>
+        <v>29</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.13</v>
+        <v>2.05</v>
       </c>
       <c r="M54" t="n">
-        <v>6.8</v>
+        <v>3.31</v>
       </c>
       <c r="N54" t="n">
-        <v>12</v>
+        <v>3.03</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7502,17 +7502,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7631,17 +7631,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="M56" t="n">
-        <v>3.55</v>
+        <v>3.07</v>
       </c>
       <c r="N56" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N57" t="n">
-        <v>3.66</v>
+        <v>6.2</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.02</v>
+        <v>2.67</v>
       </c>
       <c r="M59" t="n">
-        <v>10.2</v>
+        <v>2.98</v>
       </c>
       <c r="N59" t="n">
-        <v>29</v>
+        <v>2.44</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,16 +8061,16 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="M61" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>6.2</v>
+        <v>3.92</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z61" t="n">
         <v>1.68</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>2.05</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.44</v>
+        <v>3.65</v>
       </c>
       <c r="M62" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="N62" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,61 +11505,61 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
@@ -11572,10 +11572,10 @@
         </is>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,61 +11763,61 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
@@ -11830,10 +11830,10 @@
         </is>
       </c>
       <c r="AG88" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,61 +12150,61 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="M91" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="N91" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
@@ -12217,10 +12217,10 @@
         </is>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,61 +12408,61 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="M3" t="n">
-        <v>3.19</v>
+        <v>3.33</v>
       </c>
       <c r="N3" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.58</v>
+        <v>2.17</v>
       </c>
       <c r="M5" t="n">
-        <v>3.27</v>
+        <v>3.19</v>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>10.2</v>
       </c>
       <c r="N27" t="n">
-        <v>1.72</v>
+        <v>29</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.44</v>
+        <v>1.81</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>5.5</v>
+        <v>3.92</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.07</v>
+        <v>1.68</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="M29" t="n">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="N29" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="N30" t="n">
-        <v>2.2</v>
+        <v>3.03</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.21</v>
+        <v>1.43</v>
       </c>
       <c r="M31" t="n">
-        <v>3.01</v>
+        <v>4.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.98</v>
+        <v>6.4</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.59</v>
+        <v>2.67</v>
       </c>
       <c r="M32" t="n">
-        <v>3.56</v>
+        <v>2.98</v>
       </c>
       <c r="N32" t="n">
-        <v>4.75</v>
+        <v>2.44</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="M33" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.9</v>
+        <v>2.03</v>
       </c>
       <c r="M35" t="n">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>2.13</v>
+        <v>3.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="M36" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="N36" t="n">
-        <v>3.29</v>
+        <v>2.43</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="M38" t="n">
-        <v>4.4</v>
+        <v>3.19</v>
       </c>
       <c r="N38" t="n">
-        <v>6.4</v>
+        <v>2.94</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.47</v>
+        <v>3.65</v>
       </c>
       <c r="M39" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="M40" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N40" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z40" t="n">
         <v>1.87</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.86</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.17</v>
+        <v>4.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="N41" t="n">
-        <v>2.75</v>
+        <v>1.72</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.47</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>4.3</v>
+        <v>3.07</v>
       </c>
       <c r="N42" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.15</v>
+        <v>4.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3.19</v>
+        <v>3.95</v>
       </c>
       <c r="N44" t="n">
-        <v>2.94</v>
+        <v>1.6</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="N45" t="n">
-        <v>2.2</v>
+        <v>3.07</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,55 +6345,55 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.8</v>
+        <v>1.44</v>
       </c>
       <c r="M46" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB46" t="n">
         <v>1.6</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6470,17 +6470,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.13</v>
+        <v>3.6</v>
       </c>
       <c r="M47" t="n">
-        <v>6.8</v>
+        <v>3.55</v>
       </c>
       <c r="N47" t="n">
-        <v>12</v>
+        <v>1.92</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="M48" t="n">
-        <v>3.55</v>
+        <v>3.01</v>
       </c>
       <c r="N48" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M49" t="n">
         <v>4.3</v>
       </c>
       <c r="N49" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="N50" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7035,10 +7035,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.02</v>
+        <v>2.14</v>
       </c>
       <c r="M53" t="n">
-        <v>10.2</v>
+        <v>3.55</v>
       </c>
       <c r="N53" t="n">
-        <v>29</v>
+        <v>3.1</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,16 +7287,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="M54" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N54" t="n">
-        <v>3.03</v>
+        <v>2.13</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7502,17 +7502,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.45</v>
+        <v>1.47</v>
       </c>
       <c r="M56" t="n">
-        <v>3.07</v>
+        <v>4.3</v>
       </c>
       <c r="N56" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,16 +7674,16 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.45</v>
+        <v>3.05</v>
       </c>
       <c r="M57" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N57" t="n">
-        <v>6.2</v>
+        <v>2.2</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.12</v>
+        <v>1.59</v>
       </c>
       <c r="M58" t="n">
-        <v>3.39</v>
+        <v>3.56</v>
       </c>
       <c r="N58" t="n">
-        <v>2.84</v>
+        <v>4.75</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="M59" t="n">
-        <v>2.98</v>
+        <v>3.16</v>
       </c>
       <c r="N59" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="M61" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N61" t="n">
-        <v>3.92</v>
+        <v>5.8</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.65</v>
+        <v>1.88</v>
       </c>
       <c r="M62" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N62" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,61 +11376,61 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,61 +11505,61 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
@@ -11572,10 +11572,10 @@
         </is>
       </c>
       <c r="AG86" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="M90" t="n">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="N90" t="n">
-        <v>2.93</v>
+        <v>3.16</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,7 +12060,7 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z90" t="n">
         <v>1.6</v>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,61 +12150,61 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="M91" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="N91" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="O91" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AA91" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
@@ -12217,10 +12217,10 @@
         </is>
       </c>
       <c r="AG91" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,61 +12279,61 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="M92" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="N92" t="n">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE92" t="inlineStr">
         <is>
@@ -12346,10 +12346,10 @@
         </is>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="M110" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="N110" t="n">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14634,16 +14634,16 @@
         <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="M112" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="N112" t="n">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14892,16 +14892,16 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y112" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.68</v>
+        <v>2.42</v>
       </c>
       <c r="M126" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N126" t="n">
-        <v>4.1</v>
+        <v>2.65</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="M131" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N131" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,16 +17349,16 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z134" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,55 +17826,55 @@
         </is>
       </c>
       <c r="L135" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N135" t="n">
+        <v>4</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="n">
         <v>1.75</v>
       </c>
-      <c r="M135" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N135" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>0</v>
-      </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="M3" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="N3" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.74</v>
+        <v>2.42</v>
       </c>
       <c r="M4" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>2.46</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.08</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.01</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.29</v>
+        <v>3.08</v>
       </c>
       <c r="M22" t="n">
-        <v>5.25</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>2.01</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.02</v>
+        <v>2.14</v>
       </c>
       <c r="M27" t="n">
-        <v>10.2</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>29</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.81</v>
+        <v>1.43</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.92</v>
+        <v>6.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.17</v>
+        <v>2.51</v>
       </c>
       <c r="M29" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="N29" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.05</v>
+        <v>1.02</v>
       </c>
       <c r="M30" t="n">
-        <v>3.31</v>
+        <v>10.2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.03</v>
+        <v>29</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.43</v>
+        <v>1.84</v>
       </c>
       <c r="M31" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>6.4</v>
+        <v>3.66</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.64</v>
+        <v>2.03</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="N34" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>3.92</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="M36" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N36" t="n">
-        <v>2.43</v>
+        <v>3.03</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>3.55</v>
+        <v>3.07</v>
       </c>
       <c r="N39" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="M40" t="n">
-        <v>3.65</v>
+        <v>3.19</v>
       </c>
       <c r="N40" t="n">
-        <v>2.2</v>
+        <v>2.94</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="M42" t="n">
-        <v>3.07</v>
+        <v>3.39</v>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="M43" t="n">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>2.84</v>
+        <v>4.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.8</v>
+        <v>1.59</v>
       </c>
       <c r="M44" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="N44" t="n">
-        <v>1.6</v>
+        <v>4.75</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.22</v>
+        <v>1.47</v>
       </c>
       <c r="M45" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>3.07</v>
+        <v>4.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6341,17 +6341,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.44</v>
+        <v>3.6</v>
       </c>
       <c r="M46" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="N46" t="n">
-        <v>5.5</v>
+        <v>1.92</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6470,17 +6470,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.6</v>
+        <v>2.47</v>
       </c>
       <c r="M47" t="n">
-        <v>3.55</v>
+        <v>3.16</v>
       </c>
       <c r="N47" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.21</v>
+        <v>4.8</v>
       </c>
       <c r="M48" t="n">
-        <v>3.01</v>
+        <v>3.95</v>
       </c>
       <c r="N48" t="n">
-        <v>2.98</v>
+        <v>1.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z48" t="n">
         <v>1.95</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.75</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M49" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N49" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.13</v>
+        <v>2.21</v>
       </c>
       <c r="M51" t="n">
-        <v>6.8</v>
+        <v>3.01</v>
       </c>
       <c r="N51" t="n">
-        <v>12</v>
+        <v>2.98</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,16 +7029,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.01</v>
+        <v>3.65</v>
       </c>
       <c r="M52" t="n">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="N52" t="n">
-        <v>3.29</v>
+        <v>1.9</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.14</v>
+        <v>1.45</v>
       </c>
       <c r="M53" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N53" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="M54" t="n">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="N54" t="n">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="M56" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="N56" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7680,10 +7680,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="M57" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N57" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="M58" t="n">
-        <v>3.56</v>
+        <v>4.3</v>
       </c>
       <c r="N58" t="n">
-        <v>4.75</v>
+        <v>5.8</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.47</v>
+        <v>1.88</v>
       </c>
       <c r="M59" t="n">
-        <v>3.16</v>
+        <v>3.75</v>
       </c>
       <c r="N59" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="M61" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N61" t="n">
-        <v>5.8</v>
+        <v>2.2</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.88</v>
+        <v>2.85</v>
       </c>
       <c r="M62" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="N62" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8451,7 +8451,7 @@
         <v>1.83</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="M91" t="n">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="N91" t="n">
-        <v>2.93</v>
+        <v>3.16</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,7 +12189,7 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z91" t="n">
         <v>1.6</v>
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,61 +12279,61 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="M92" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="N92" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="O92" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AA92" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE92" t="inlineStr">
         <is>
@@ -12346,10 +12346,10 @@
         </is>
       </c>
       <c r="AG92" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,61 +12408,61 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,43 +14601,43 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="M110" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="N110" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S110" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T110" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U110" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V110" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W110" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y110" t="n">
         <v>2.38</v>
@@ -14646,16 +14646,16 @@
         <v>1.53</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD110" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE110" t="inlineStr">
         <is>
@@ -14668,10 +14668,10 @@
         </is>
       </c>
       <c r="AG110" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH110" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,43 +14730,43 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="M111" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="N111" t="n">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="O111" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U111" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y111" t="n">
         <v>2.38</v>
@@ -14775,16 +14775,16 @@
         <v>1.53</v>
       </c>
       <c r="AA111" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AD111" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE111" t="inlineStr">
         <is>
@@ -14797,10 +14797,10 @@
         </is>
       </c>
       <c r="AG111" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH111" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.68</v>
+        <v>2.42</v>
       </c>
       <c r="M127" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N127" t="n">
-        <v>4.1</v>
+        <v>2.65</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17355,10 +17355,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17484,10 +17484,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="M133" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="N133" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,16 +17607,16 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA133" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M135" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N135" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17865,16 +17865,16 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB135" t="n">
         <v>1.75</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -17955,13 +17955,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="M136" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N136" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -17994,10 +17994,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="Z136" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18084,13 +18084,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="M137" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N137" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18123,10 +18123,10 @@
         <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="Z137" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AA137" t="n">
         <v>0</v>

--- a/jogos_2025-09-06.xlsx
+++ b/jogos_2025-09-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK138"/>
+  <dimension ref="A1:AK141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="M4" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="N4" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.74</v>
+        <v>2.42</v>
       </c>
       <c r="M7" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>2.46</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45906.33333333334</v>
+        <v>45906.29166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.82</v>
+        <v>2.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45906.33333333334</v>
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45906.35416666666</v>
+        <v>45906.33333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45906.375</v>
+        <v>45906.35416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45906.38541666666</v>
+        <v>45906.375</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45906.39583333334</v>
+        <v>45906.38541666666</v>
       </c>
     </row>
     <row r="22">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.08</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.01</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45906.41666666666</v>
+        <v>45906.39583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45906.45833333334</v>
+        <v>45906.41666666666</v>
       </c>
     </row>
     <row r="28">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.43</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>3.07</v>
       </c>
       <c r="N28" t="n">
-        <v>6.4</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.51</v>
+        <v>1.84</v>
       </c>
       <c r="M29" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.43</v>
+        <v>3.66</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4277,17 +4277,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="M30" t="n">
-        <v>10.2</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>29</v>
+        <v>1.92</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.84</v>
+        <v>2.9</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="N31" t="n">
-        <v>3.66</v>
+        <v>2.13</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4584,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>3.19</v>
       </c>
       <c r="N33" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.81</v>
+        <v>2.21</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="N35" t="n">
-        <v>3.92</v>
+        <v>2.98</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="M36" t="n">
-        <v>3.31</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3.03</v>
+        <v>5.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.84</v>
+        <v>2.07</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.67</v>
+        <v>2.01</v>
       </c>
       <c r="M37" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="N37" t="n">
-        <v>2.44</v>
+        <v>3.29</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="M39" t="n">
-        <v>3.07</v>
+        <v>3.39</v>
       </c>
       <c r="N39" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="M40" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="N40" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.2</v>
+        <v>1.45</v>
       </c>
       <c r="M41" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="N41" t="n">
-        <v>1.72</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="M42" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="N42" t="n">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N43" t="n">
-        <v>4.6</v>
+        <v>3.03</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.47</v>
+        <v>2.67</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>2.98</v>
       </c>
       <c r="N45" t="n">
-        <v>4.7</v>
+        <v>2.44</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6341,17 +6341,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="M46" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N46" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.47</v>
+        <v>2.22</v>
       </c>
       <c r="M47" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="N47" t="n">
-        <v>2.5</v>
+        <v>3.07</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6507,16 +6507,16 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>4.8</v>
+        <v>2.17</v>
       </c>
       <c r="M48" t="n">
-        <v>3.95</v>
+        <v>3.38</v>
       </c>
       <c r="N48" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="M49" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.21</v>
+        <v>1.02</v>
       </c>
       <c r="M51" t="n">
-        <v>3.01</v>
+        <v>10.2</v>
       </c>
       <c r="N51" t="n">
-        <v>2.98</v>
+        <v>29</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,16 +7029,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.65</v>
+        <v>1.88</v>
       </c>
       <c r="M52" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N52" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.45</v>
+        <v>4.8</v>
       </c>
       <c r="M53" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N53" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="M55" t="n">
-        <v>3.14</v>
+        <v>3.56</v>
       </c>
       <c r="N55" t="n">
-        <v>3.29</v>
+        <v>4.75</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="M56" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="N56" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,16 +7674,16 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="M57" t="n">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="N57" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.44</v>
+        <v>2.51</v>
       </c>
       <c r="M58" t="n">
-        <v>4.3</v>
+        <v>3.23</v>
       </c>
       <c r="N58" t="n">
-        <v>5.8</v>
+        <v>2.43</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="M59" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N59" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.22</v>
+        <v>1.81</v>
       </c>
       <c r="M60" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>3.07</v>
+        <v>3.92</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="M61" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N61" t="n">
         <v>2.2</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.85</v>
+        <v>1.64</v>
       </c>
       <c r="M62" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8497,27 +8497,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="M63" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N63" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,16 +8577,16 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45906.46875</v>
+        <v>45906.45833333334</v>
       </c>
     </row>
     <row r="64">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45906.47916666666</v>
+        <v>45906.46875</v>
       </c>
     </row>
     <row r="65">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45906.5</v>
+        <v>45906.47916666666</v>
       </c>
     </row>
     <row r="69">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45906.52083333334</v>
+        <v>45906.5</v>
       </c>
     </row>
     <row r="79">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11335,12 +11335,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,61 +11376,61 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="AG85" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45906.54166666666</v>
+        <v>45906.52083333334</v>
       </c>
     </row>
     <row r="86">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,61 +11505,61 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
@@ -11572,10 +11572,10 @@
         </is>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11851,27 +11851,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45906.5625</v>
+        <v>45906.54166666666</v>
       </c>
     </row>
     <row r="90">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="M92" t="n">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="N92" t="n">
-        <v>2.93</v>
+        <v>3.16</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,7 +12318,7 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z92" t="n">
         <v>1.6</v>
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,61 +12408,61 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="M93" t="n">
-        <v>3.14</v>
+        <v>3.31</v>
       </c>
       <c r="N93" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="O93" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA93" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12625,27 +12625,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,61 +12666,61 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE95" t="inlineStr">
         <is>
@@ -12733,10 +12733,10 @@
         </is>
       </c>
       <c r="AG95" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH95" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI95" t="n">
         <v>0</v>
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45906.58333333334</v>
+        <v>45906.5625</v>
       </c>
     </row>
     <row r="96">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45906.60416666666</v>
+        <v>45906.58333333334</v>
       </c>
     </row>
     <row r="100">
@@ -13270,12 +13270,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45906.625</v>
+        <v>45906.58333333334</v>
       </c>
     </row>
     <row r="101">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45906.625</v>
+        <v>45906.60416666666</v>
       </c>
     </row>
     <row r="102">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45906.64583333334</v>
+        <v>45906.625</v>
       </c>
     </row>
     <row r="105">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45906.64583333334</v>
+        <v>45906.625</v>
       </c>
     </row>
     <row r="106">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14560,27 +14560,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,61 +14601,61 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U110" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V110" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AD110" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE110" t="inlineStr">
         <is>
@@ -14668,10 +14668,10 @@
         </is>
       </c>
       <c r="AG110" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH110" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45906.66666666666</v>
+        <v>45906.64583333334</v>
       </c>
     </row>
     <row r="111">
@@ -14689,27 +14689,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45906.66666666666</v>
+        <v>45906.64583333334</v>
       </c>
     </row>
     <row r="112">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3.85</v>
+        <v>2.19</v>
       </c>
       <c r="M112" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N112" t="n">
-        <v>1.96</v>
+        <v>3.28</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14892,16 +14892,16 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,61 +14988,61 @@
         </is>
       </c>
       <c r="L113" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M113" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N113" t="n">
         <v>2.19</v>
       </c>
-      <c r="M113" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N113" t="n">
-        <v>3.28</v>
-      </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W113" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y113" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
@@ -15055,10 +15055,10 @@
         </is>
       </c>
       <c r="AG113" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH113" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
@@ -15076,27 +15076,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45906.6875</v>
+        <v>45906.66666666666</v>
       </c>
     </row>
     <row r="115">
@@ -15205,27 +15205,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="M115" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N115" t="n">
-        <v>2.85</v>
+        <v>1.96</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15279,16 +15279,16 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45906.6875</v>
+        <v>45906.66666666666</v>
       </c>
     </row>
     <row r="116">
@@ -15334,27 +15334,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45906.70833333334</v>
+        <v>45906.67708333334</v>
       </c>
     </row>
     <row r="117">
@@ -15463,27 +15463,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45906.70833333334</v>
+        <v>45906.6875</v>
       </c>
     </row>
     <row r="118">
@@ -15592,27 +15592,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45906.70833333334</v>
+        <v>45906.6875</v>
       </c>
     </row>
     <row r="119">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,61 +16149,61 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X122" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="inlineStr">
         <is>
@@ -16216,10 +16216,10 @@
         </is>
       </c>
       <c r="AG122" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH122" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45906.77083333334</v>
+        <v>45906.70833333334</v>
       </c>
     </row>
     <row r="123">
@@ -16237,12 +16237,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45906.83333333334</v>
+        <v>45906.70833333334</v>
       </c>
     </row>
     <row r="124">
@@ -16366,12 +16366,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45906.83333333334</v>
+        <v>45906.70833333334</v>
       </c>
     </row>
     <row r="125">
@@ -16495,12 +16495,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,61 +16536,61 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S125" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T125" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U125" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V125" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W125" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X125" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD125" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE125" t="inlineStr">
         <is>
@@ -16603,10 +16603,10 @@
         </is>
       </c>
       <c r="AG125" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH125" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI125" t="n">
         <v>0</v>
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45906.83333333334</v>
+        <v>45906.77083333334</v>
       </c>
     </row>
     <row r="126">
@@ -16624,7 +16624,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45906.85416666666</v>
+        <v>45906.83333333334</v>
       </c>
     </row>
     <row r="127">
@@ -16753,12 +16753,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16873,7 +16873,7 @@
         <v>0</v>
       </c>
       <c r="AK127" s="3" t="n">
-        <v>45906.85416666666</v>
+        <v>45906.83333333334</v>
       </c>
     </row>
     <row r="128">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45906.85416666666</v>
+        <v>45906.83333333334</v>
       </c>
     </row>
     <row r="129">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="M129" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="N129" t="n">
-        <v>4.1</v>
+        <v>5.26</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45906.875</v>
+        <v>45906.85416666666</v>
       </c>
     </row>
     <row r="131">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45906.89583333334</v>
+        <v>45906.85416666666</v>
       </c>
     </row>
     <row r="132">
@@ -17398,12 +17398,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="M132" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="N132" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,16 +17478,16 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -17518,7 +17518,7 @@
         <v>0</v>
       </c>
       <c r="AK132" s="3" t="n">
-        <v>45906.89583333334</v>
+        <v>45906.85416666666</v>
       </c>
     </row>
     <row r="133">
@@ -17527,12 +17527,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17647,7 +17647,7 @@
         <v>0</v>
       </c>
       <c r="AK133" s="3" t="n">
-        <v>45906.89583333334</v>
+        <v>45906.875</v>
       </c>
     </row>
     <row r="134">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="M134" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N134" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,16 +17736,16 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="M135" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="N135" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17871,10 +17871,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -17914,7 +17914,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -17955,13 +17955,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.56</v>
+        <v>2.05</v>
       </c>
       <c r="M136" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N136" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
         <v>1.8</v>
       </c>
       <c r="Z136" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -18034,7 +18034,7 @@
         <v>0</v>
       </c>
       <c r="AK136" s="3" t="n">
-        <v>45906.91666666666</v>
+        <v>45906.89583333334</v>
       </c>
     </row>
     <row r="137">
@@ -18043,12 +18043,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18084,13 +18084,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18123,10 +18123,10 @@
         <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA137" t="n">
         <v>0</v>
@@ -18163,7 +18163,7 @@
         <v>0</v>
       </c>
       <c r="AK137" s="3" t="n">
-        <v>45906.91666666666</v>
+        <v>45906.89583333334</v>
       </c>
     </row>
     <row r="138">
@@ -18172,126 +18172,513 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Birmingham Legion</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M138" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N138" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK138" s="3" t="n">
+        <v>45906.89583333334</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45906</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Colorado Springs</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M139" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N139" t="n">
+        <v>4.9</v